--- a/instruction_data/templates/province_lookup.xlsx
+++ b/instruction_data/templates/province_lookup.xlsx
@@ -8,16 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyle/projects/onesky_financial_agent/instruction_data/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61E7D6A6-3E5A-C84F-B7CB-D56A700FB293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8956E94-7098-9D49-BE90-DB54505EB984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{7FDE426A-E8F3-2549-B987-AA4B5E1E483E}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{7FDE426A-E8F3-2549-B987-AA4B5E1E483E}"/>
   </bookViews>
   <sheets>
     <sheet name="province_lookup" sheetId="1" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId2"/>
-  </externalReferences>
   <definedNames>
     <definedName name="CHActCashBalance">#REF!</definedName>
     <definedName name="CHExpenseForcast">#REF!</definedName>
@@ -69,7 +66,7 @@
     <definedName name="YTDCashBalance">#REF!</definedName>
     <definedName name="YTDMonthOfCash">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -90,80 +87,44 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>Cao Bang</t>
   </si>
   <si>
-    <t>MOET BG</t>
-  </si>
-  <si>
     <t>Bac Giang MOET</t>
   </si>
   <si>
-    <t>MOET BN</t>
-  </si>
-  <si>
     <t>Bac Ninh MOET</t>
   </si>
   <si>
-    <t>MOET BD</t>
-  </si>
-  <si>
     <t>Binh Duong MOET</t>
   </si>
   <si>
-    <t>MOET HCM</t>
-  </si>
-  <si>
     <t>HCM MOET</t>
   </si>
   <si>
-    <t>MOET LA</t>
-  </si>
-  <si>
     <t>Long An MOET</t>
   </si>
   <si>
-    <t>MOET</t>
-  </si>
-  <si>
     <t>Preparation and general of MOET</t>
   </si>
   <si>
-    <t>QNg ICC</t>
-  </si>
-  <si>
     <t>Quang Ngai ICC</t>
   </si>
   <si>
-    <t>HD ICC</t>
-  </si>
-  <si>
     <t>Hai Duong ICC</t>
   </si>
   <si>
-    <t>QN ICC</t>
-  </si>
-  <si>
     <t>Quang Nam ICC</t>
   </si>
   <si>
-    <t>DN ICC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Da Nang ICC </t>
   </si>
   <si>
-    <t>General VN</t>
-  </si>
-  <si>
     <t>VN General National Training</t>
   </si>
   <si>
-    <t>In support</t>
-  </si>
-  <si>
     <t>In-country program support</t>
   </si>
   <si>
@@ -174,6 +135,48 @@
   </si>
   <si>
     <t>Provincial Lookup Table</t>
+  </si>
+  <si>
+    <t>ELC</t>
+  </si>
+  <si>
+    <t>VNELC</t>
+  </si>
+  <si>
+    <t>VNOther</t>
+  </si>
+  <si>
+    <t>VNHBC</t>
+  </si>
+  <si>
+    <t>VNDN</t>
+  </si>
+  <si>
+    <t>VNQN</t>
+  </si>
+  <si>
+    <t>VNHD</t>
+  </si>
+  <si>
+    <t>VNQNg</t>
+  </si>
+  <si>
+    <t>VNMOET</t>
+  </si>
+  <si>
+    <t>VNLA</t>
+  </si>
+  <si>
+    <t>VNHCM</t>
+  </si>
+  <si>
+    <t>VNBD</t>
+  </si>
+  <si>
+    <t>VNBN</t>
+  </si>
+  <si>
+    <t>VNBG</t>
   </si>
 </sst>
 </file>
@@ -220,7 +223,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -233,8 +236,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -265,14 +274,23 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
         <color indexed="64"/>
-      </top>
-      <bottom/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -281,9 +299,8 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -293,10 +310,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -316,44 +335,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Notes"/>
-      <sheetName val="Output (Oct)"/>
-      <sheetName val="Output(link)"/>
-      <sheetName val="(1a)Transactions"/>
-      <sheetName val="(1b)PIT+SI"/>
-      <sheetName val="(1c)manual input"/>
-      <sheetName val="1230"/>
-      <sheetName val="1500"/>
-      <sheetName val="1252"/>
-      <sheetName val="30 Bank (VND)"/>
-      <sheetName val="29 Bank (USD)"/>
-      <sheetName val="Lookup2_Allocation"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -673,138 +654,134 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02A9EBC3-B14A-A744-AF74-4987BAF8B322}">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" s="6">
+      <c r="A1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="4"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="1"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="B15" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="1"/>
+      <c r="B16" s="7" t="s">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
